--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -1327,7 +1327,7 @@
         <v>136298255</v>
       </c>
       <c r="B8" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -1327,7 +1327,7 @@
         <v>136298255</v>
       </c>
       <c r="B8" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -1327,7 +1327,7 @@
         <v>136298255</v>
       </c>
       <c r="B8" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -1327,7 +1327,7 @@
         <v>136298255</v>
       </c>
       <c r="B8" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
